--- a/AAII_Financials/Quarterly/TELFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>TELFY</t>
   </si>
@@ -655,56 +655,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -732,8 +735,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -761,8 +767,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -790,8 +799,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -803,8 +815,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -832,8 +845,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -861,8 +877,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -890,8 +909,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -919,8 +941,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -929,8 +954,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -958,8 +984,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -987,8 +1016,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1000,8 +1032,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1029,8 +1062,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1058,8 +1094,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1087,8 +1126,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1116,8 +1158,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1145,8 +1190,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1174,8 +1222,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1203,8 +1254,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1232,8 +1286,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1261,8 +1318,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1290,8 +1350,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1319,8 +1382,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1348,8 +1414,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1377,8 +1446,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1406,8 +1478,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1435,8 +1510,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1464,42 +1542,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1511,8 +1595,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1524,269 +1609,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5882600</v>
+      </c>
+      <c r="E41" s="3">
         <v>7706900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7639500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8346600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5644500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7904300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8275800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7958500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7971500</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>607800</v>
+      </c>
+      <c r="E42" s="3">
         <v>443800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>52800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>449300</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>515100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10524400</v>
+      </c>
+      <c r="E43" s="3">
         <v>9990600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11233100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9996900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10652500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9966800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11649000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9417000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11399400</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1019100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1012100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1032300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>987700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1056500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1026900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1879800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1648500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1750300</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4471600</v>
+      </c>
+      <c r="E45" s="3">
         <v>5046400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2921900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1765200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2938000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1869100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1995100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2960700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2446800</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22659700</v>
+      </c>
+      <c r="E46" s="3">
         <v>25836600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24968900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23158700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22127900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22942400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23799700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23281700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23568000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7831600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9122900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10082200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10323000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10249700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11077700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11568600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13244500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12309900</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29033500</v>
+      </c>
+      <c r="E48" s="3">
         <v>30056400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30925400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30382000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32131100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34698800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33845300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35091700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34774000</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28955800</v>
+      </c>
+      <c r="E49" s="3">
         <v>29245000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30620100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27265800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>30535700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>33246400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32189900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>33662700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>32955200</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1814,8 +1927,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1843,37 +1959,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4308200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4179900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4925400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3716700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5152700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3948300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8632500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5859200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8833100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1901,37 +2023,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101219000</v>
+      </c>
+      <c r="E54" s="3">
         <v>108039200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110826800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>104050100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109089300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115313400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115672100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118962900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117695600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1943,8 +2071,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1956,182 +2085,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6405800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7620100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7933100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8057800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7982400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8413800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>8315500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7087900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7229100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9754600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8091900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7112400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6565700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6447900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6973800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6781800</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8065800</v>
+      </c>
+      <c r="E59" s="3">
         <v>12466800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10300600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9116900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9535000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8842700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18605000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9674700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19715300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24616700</v>
+      </c>
+      <c r="E60" s="3">
         <v>29161700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29506800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26642500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25897400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25863800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25052900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26158300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26497200</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>40546100</v>
+      </c>
+      <c r="E61" s="3">
         <v>41991300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42735200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>40655300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42469700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44288700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43358400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44267500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44098200</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9360200</v>
+      </c>
+      <c r="E62" s="3">
         <v>9337800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6870200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6359900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6900200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7369300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10562000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6032800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11026700</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2159,8 +2307,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2188,8 +2339,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2217,37 +2371,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>80294800</v>
+      </c>
+      <c r="E66" s="3">
         <v>87130400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86195000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80498000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82567200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85363100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82134800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>84914800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84969600</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2259,8 +2419,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2288,8 +2449,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2317,8 +2481,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2346,8 +2513,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2375,37 +2545,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18550200</v>
+      </c>
+      <c r="E72" s="3">
         <v>20729100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24216100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24597800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26847700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28688000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>30177900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2433,8 +2609,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2462,8 +2641,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2491,37 +2673,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16765700</v>
+      </c>
+      <c r="E76" s="3">
         <v>16740600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20297100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20030000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22517900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24153900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27109400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27352600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26111500</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2549,42 +2737,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2612,8 +2806,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2625,37 +2822,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
         <v>907500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3107500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1007600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2337000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>843200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2939800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>987900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2342800</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2683,8 +2884,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2712,8 +2916,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2741,8 +2948,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2770,8 +2980,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2799,37 +3012,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2425500</v>
+      </c>
+      <c r="E89" s="3">
         <v>3832300</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3">
         <v>3770300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3121300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3262000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2841,37 +3060,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1508100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1681300</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1824900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1436300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1902800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1523300</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2899,8 +3122,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2928,37 +3154,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1719400</v>
+      </c>
+      <c r="E94" s="3">
         <v>486100</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1260100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2111600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1055700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-199900</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2970,37 +3202,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>838600</v>
+      </c>
+      <c r="E96" s="3">
         <v>772600</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>374700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>539800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>771800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>157500</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3028,8 +3264,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3057,8 +3296,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3086,75 +3328,84 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2055300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1797600</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3069500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-329200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2259800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2203400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3">
         <v>-164700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-131200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-146400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>56900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-22000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1096800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2648800</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
@@ -3162,15 +3413,18 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-724000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>549300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100000</v>
       </c>
     </row>
